--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_744_Svalbard_Isl_Norway.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_744_Svalbard_Isl_Norway.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R04a3efb199cb4672"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R0c4d814fab424a07"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R6a1bed26340742b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rffcd57d6ccaf41e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R5c0d23b2d58840cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R2cee186f2b3248a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rd157a67720d64e3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rbf1bd97bb4174590"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R0992e0becb634e10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rd5eb6a8325834381"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R3a8ff7bbfc0c4aff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R13cfae622be74017"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ744CommercialTable" displayName="EEZ744CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ744CommercialTable" displayName="EEZ744CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ744FunctionalTable" displayName="EEZ744FunctionalTable" ref="A1:O17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O17"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ744FunctionalTable" displayName="EEZ744FunctionalTable" ref="A1:E17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E17"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ744ValidationTable" displayName="EEZ744ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ744ValidationTable" displayName="EEZ744ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -4848,7 +4802,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5c890272e4774b84"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbaac0500da7f488c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4858,20 +4812,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4879,606 +4823,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>149629.0587463644</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.081914828956371</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>1207.5769896422073</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>149629.0587463644</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>1209.9448080419281</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$63,A2,'Species'!$U$2:$U$63))</x:f>
-        <x:v>181042902.76236427</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.081914828956371</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>1207.5769896422073</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>180688608.32393172</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>354294.43843254447</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0019608011911707</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.001960801191170717</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1779.6654990480001</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.4134358204738224</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>259.08115259926404</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1779.6654990480001</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>294.80251467360944</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$63,A3,'Species'!$U$2:$U$63))</x:f>
-        <x:v>524649.8643972145</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.4134358204738224</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>259.08115259926404</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>461077.7887345003</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>63572.0756627142</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.137877115783863</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.13787711578386294</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>9487.985060291101</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.356112613140154</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2270.453507192784</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>9487.985060291101</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2318.227250535651</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$63,A4,'Species'!$U$2:$U$63))</x:f>
-        <x:v>21995305.51944197</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.356112613140154</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2270.453507192784</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>21542028.95633067</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>453276.5631113015</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0210414981815394</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.02104149818153943</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>5060.165295037599</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.3800000000000003</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>239.88329190194924</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>5060.165295037599</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>239.88329190194898</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$63,A5,'Species'!$U$2:$U$63))</x:f>
-        <x:v>1213849.1085416162</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.3800000000000003</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>239.88329190194924</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>1213849.1085416174</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>-1.1641532182693481e-9</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>0.999999999999999</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>-9.590592521569863e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>46.41804919729999</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.5794089801205695</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>37.967235851311735</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>46.41804919729999</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>58.44146501149093</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$63,A6,'Species'!$U$2:$U$63))</x:f>
-        <x:v>2712.738798065672</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.5794089801205695</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>37.967235851311735</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>1762.3650216316803</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>950.3737764339919</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.53926046237237</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.5392604623723701</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>44212.8240257056</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.279005806182865</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>190.11036960461826</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>44212.8240257056</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>190.43294571206548</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$63,A7,'Species'!$U$2:$U$63))</x:f>
-        <x:v>8419578.3174643</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.279005806182865</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>190.11036960461826</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>8405316.316790838</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>14262.000673461705</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.001696783337585</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.001696783337584963</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>5588.196772855699</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.694949327878268</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>495.39238659850315</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>5588.196772855699</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>506.65451098240123</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$63,A8,'Species'!$U$2:$U$63))</x:f>
-        <x:v>2831285.103224637</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.694949327878268</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>495.39238659850315</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>2768350.136087038</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>62934.9671375989</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0227337453876246</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.022733745387624696</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Salmon, smelts, etc</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>1.2174987506000001</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.1523481610117385</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>142.01955941556372</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>1.2174987506000001</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>142.1885415955389</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$63,A9,'Species'!$U$2:$U$63))</x:f>
-        <x:v>173.11437174220478</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.1523481610117385</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>142.01955941556372</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>172.9086361492113</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>0.2057355929934772</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0011898514589863</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.0011898514589863396</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>4084.377305324899</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.718239438802443</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>522.684280167765</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>4084.377305324899</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>559.4033698089713</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$63,A10,'Species'!$U$2:$U$63))</x:f>
-        <x:v>2284814.428170034</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.718239438802443</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>522.684280167765</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>2134839.8117673006</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>149974.6164027336</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.070250992873596</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.07025099287359597</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>1.5415751947</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.637792142590448</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>434.3023132637712</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>1.5415751947</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>440.90463850093937</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$63,A11,'Species'!$U$2:$U$63))</x:f>
-        <x:v>679.6876539412187</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.637792142590448</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>434.3023132637712</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>669.5096731282586</x:v>
       </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>10.177980812960186</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0152021415395</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.01520214153950003</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa91f32324d04b50"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1fc1f303e7344f75"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5488,20 +5038,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -5509,930 +5049,326 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>79.2038338829</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>4.35</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>2238.7211385683377</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>79.2038338829</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>2238.7211385683377</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$63,A2,'Species'!$U$2:$U$63))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>177315.29716930338</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>4.35</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>2238.7211385683377</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>177315.29716930338</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>132333.825454321</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.079371768003379</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>1200.5265471060738</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>132333.825454321</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>1209.5457431626876</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$63,A3,'Species'!$U$2:$U$63))</x:f>
-        <x:v>160063815.25470808</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.079371768003379</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>1200.5265471060738</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>158870270.53801385</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>1193544.7166942358</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.007512700221711</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.00751270022171108</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>1563.0853251627</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.659652323854231</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>456.72241230902546</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>1563.0853251627</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>620.2971201627731</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$63,A4,'Species'!$U$2:$U$63))</x:f>
-        <x:v>969577.3257671146</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.659652323854231</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>456.72241230902546</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>713896.1003531457</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>255681.2254139689</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.3581490713949693</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.3581490713949692</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large flatfishes (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>0.0592103833</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.26</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>181.97008586099827</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>0.0592103833</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>181.97008586099827</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$63,A5,'Species'!$U$2:$U$63))</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>10.774518532963619</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.26</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>181.97008586099827</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
-        <x:v>10.774518532963619</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>1.5415751947</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.637792142590448</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>434.3023132637712</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>1.5415751947</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>440.90463850093937</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$63,A6,'Species'!$U$2:$U$63))</x:f>
-        <x:v>679.6876539412187</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.637792142590448</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>434.3023132637712</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>669.5096731282586</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>10.177980812960186</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0152021415395</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.01520214153950003</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>44.1857756457</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.7900000000000005</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>616.5950018614828</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>44.1857756457</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>616.5950018614822</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$63,A7,'Species'!$U$2:$U$63))</x:f>
-        <x:v>27244.72841651142</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.7900000000000005</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>616.5950018614828</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>27244.728416511454</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>-3.2741809263825417e-11</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>0.9999999999999988</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>-1.2017667698233506e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>1474.1793658769</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.5047212255003326</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>319.6842391392015</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>1474.1793658769</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>335.20877685498544</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$63,A8,'Species'!$U$2:$U$63))</x:f>
-        <x:v>494157.8621004537</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.5047212255003326</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>319.6842391392015</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>471271.9089350673</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>22885.953165386396</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0485620991437867</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.048562099143786785</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>1.9846739612</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.041846839276706</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1101.1509030146135</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>1.9846739612</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1624.5435673280303</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$63,A9,'Species'!$U$2:$U$63))</x:f>
-        <x:v>3224.1893169109007</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.041846839276706</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1101.1509030146135</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>2185.42552456497</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>1038.7637923459306</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.4753142034216455</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.47531420342164554</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>3322.1341338069997</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.65</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>446.683592150963</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>3322.1341338069997</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>446.683592150963</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$63,A10,'Species'!$U$2:$U$63))</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>1483942.8084962387</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.65</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>446.683592150963</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
-        <x:v>1483942.8084962387</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>1304.0747746595002</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.0496405540198825</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1121.0901943604956</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>1304.0747746595002</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1136.010448112292</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$63,A11,'Species'!$U$2:$U$63))</x:f>
-        <x:v>1481442.569132875</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.0496405540198825</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1121.0901943604956</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>1461985.4425836387</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>19457.126549236244</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0133087006084351</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.013308700608435177</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>64812.5625648365</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.517248582311828</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>329.03991348534043</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>64812.5625648365</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>468.58652866964036</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$63,A12,'Species'!$U$2:$U$63))</x:f>
-        <x:v>30370293.70644062</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.517248582311828</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>329.03991348534043</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>21325919.979097016</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>9044373.727343604</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.4241023944668558</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.4241023944668558</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>5060.165295037599</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.3800000000000003</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>239.88329190194924</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>5060.165295037599</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>239.88329190194898</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$63,A13,'Species'!$U$2:$U$63))</x:f>
-        <x:v>1213849.1085416162</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.3800000000000003</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>239.88329190194924</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>1213849.1085416174</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>-1.1641532182693481e-9</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>0.999999999999999</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>-9.590592521569863e-16</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>99.8351801308</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>2.5422274534110687</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>34.85197978101731</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>99.8351801308</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>44.48315842852196</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$63,A14,'Species'!$U$2:$U$63))</x:f>
-        <x:v>4440.984134498404</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>2.5422274534110687</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>34.85197978101731</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>3479.4536793528628</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>961.5304551455415</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.2763452380042533</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.27634523800425326</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>305.4861331711</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.9729213555490785</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>93.95531556679363</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>305.4861331711</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>99.81468546620602</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$63,A15,'Species'!$U$2:$U$63))</x:f>
-        <x:v>30492.00229676087</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.9729213555490785</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>93.95531556679363</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>28702.046043370243</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>1789.9562533906283</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.0623633677782383</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.06236336777823831</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>1.2006817912</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.15</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>141.2537544622754</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>1.2006817912</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>141.2537544622754</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$63,A16,'Species'!$U$2:$U$63))</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>169.60081092148982</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.15</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>141.2537544622754</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
-        <x:v>169.60081092148982</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>9487.9258499078</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>4.356119453544368</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>2270.489268508424</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>9487.9258499078</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>2318.240582069597</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$63,A17,'Species'!$U$2:$U$63))</x:f>
-        <x:v>21995294.744923435</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>4.356119453544368</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>2270.489268508424</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>21542233.82261933</x:v>
       </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>453060.922304105</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0210312879358125</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.021031287935812458</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G17">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O17">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3faade2e04a34c30"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9c5ad46d435c46be"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6607,7 +5543,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -6706,7 +5642,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>218315950.64442784</x:v>
+        <x:v>217216675.2255146</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6720,7 +5656,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>218315950.6444278</x:v>
+        <x:v>207323146.5444756</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6734,7 +5670,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>-2.9802322387695312e-8</x:v>
+        <x:v>-1099275.418913275</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6748,7 +5684,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-5.960464477539063e-8</x:v>
+        <x:v>-10992804.09995228</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6759,9 +5695,9 @@
         <x:v>EEZ_744</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -6773,47 +5709,19 @@
         <x:v>EEZ_744</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_744</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_744</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4097f87680db4a1e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra4311363ca144af3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6860,7 +5768,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
